--- a/Proyecto Interno/food-security-paper/output/figures/fig_afford_cost_exp_ratio.xlsx
+++ b/Proyecto Interno/food-security-paper/output/figures/fig_afford_cost_exp_ratio.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="E3">
-        <v>1.332401621880708</v>
+        <v>1.346928307230373</v>
       </c>
       <c r="F3">
-        <v>1.332401621880708</v>
+        <v>1.346928307230373</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="E6">
-        <v>1.596367504584316</v>
+        <v>1.613847328224782</v>
       </c>
       <c r="F6">
-        <v>1.596367504584316</v>
+        <v>1.613847328224782</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="E9">
-        <v>1.222554515846119</v>
+        <v>1.23676210224399</v>
       </c>
       <c r="F9">
-        <v>1.222554515846119</v>
+        <v>1.23676210224399</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.382864351603256</v>
+        <v>1.39814363108671</v>
       </c>
       <c r="F12">
-        <v>1.382864351603256</v>
+        <v>1.39814363108671</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="E15">
-        <v>1.094417593326545</v>
+        <v>1.105518374852383</v>
       </c>
       <c r="F15">
-        <v>1.094417593326545</v>
+        <v>1.105518374852383</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="E18">
-        <v>1.378089260854854</v>
+        <v>1.391670165804263</v>
       </c>
       <c r="F18">
-        <v>1.378089260854854</v>
+        <v>1.391670165804263</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="E21">
-        <v>1.092697602642947</v>
+        <v>1.104290011149934</v>
       </c>
       <c r="F21">
-        <v>1.092697602642947</v>
+        <v>1.104290011149934</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="E24">
-        <v>1.251823832687784</v>
+        <v>1.265226653940198</v>
       </c>
       <c r="F24">
-        <v>1.251823832687784</v>
+        <v>1.265226653940198</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="E27">
-        <v>1.182131759706541</v>
+        <v>1.195461015424477</v>
       </c>
       <c r="F27">
-        <v>1.182131759706541</v>
+        <v>1.195461015424477</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="E30">
-        <v>1.031961940197676</v>
+        <v>1.044398253752695</v>
       </c>
       <c r="F30">
-        <v>1.031961940197676</v>
+        <v>1.044398253752695</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="E33">
-        <v>1.302622459572188</v>
+        <v>1.318876160484645</v>
       </c>
       <c r="F33">
-        <v>1.302622459572188</v>
+        <v>1.318876160484645</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="E36">
-        <v>1.198894954563957</v>
+        <v>1.214728716810014</v>
       </c>
       <c r="F36">
-        <v>1.198894954563957</v>
+        <v>1.214728716810014</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="E39">
-        <v>1.277129869016355</v>
+        <v>1.293753128313997</v>
       </c>
       <c r="F39">
-        <v>1.277129869016355</v>
+        <v>1.293753128313997</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="E42">
-        <v>1.278184262701975</v>
+        <v>1.294731507567422</v>
       </c>
       <c r="F42">
-        <v>1.278184262701975</v>
+        <v>1.294731507567422</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="E45">
-        <v>3.104508267256227</v>
+        <v>3.142277777525784</v>
       </c>
       <c r="F45">
-        <v>3.104508267256227</v>
+        <v>3.142277777525784</v>
       </c>
       <c r="G45" t="b">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>142.3712338531594</v>
+        <v>144.0689054858252</v>
       </c>
       <c r="F48">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="E51">
-        <v>263.1482808980476</v>
+        <v>266.0140373265538</v>
       </c>
       <c r="F51">
         <v>5</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E54">
-        <v>52.63255868138875</v>
+        <v>53.16605385086122</v>
       </c>
       <c r="F54">
         <v>5</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="E57">
-        <v>34.81968497776113</v>
+        <v>35.17232618345506</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="E60">
-        <v>3.379414241904313</v>
+        <v>3.414981762026402</v>
       </c>
       <c r="F60">
-        <v>3.379414241904313</v>
+        <v>3.414981762026402</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="E63">
-        <v>4.282744987328559</v>
+        <v>4.327739353424454</v>
       </c>
       <c r="F63">
-        <v>4.282744987328559</v>
+        <v>4.327739353424454</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="E66">
-        <v>2.485720177128676</v>
+        <v>2.51272309837254</v>
       </c>
       <c r="F66">
-        <v>2.485720177128676</v>
+        <v>2.51272309837254</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="E69">
-        <v>1.978967972499749</v>
+        <v>2.000857853883947</v>
       </c>
       <c r="F69">
-        <v>1.978967972499749</v>
+        <v>2.000857853883947</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="E72">
-        <v>2.316472077930089</v>
+        <v>2.340888838943124</v>
       </c>
       <c r="F72">
-        <v>2.316472077930089</v>
+        <v>2.340888838943124</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="E75">
-        <v>3.407526249010842</v>
+        <v>3.443252405764575</v>
       </c>
       <c r="F75">
-        <v>3.407526249010842</v>
+        <v>3.443252405764575</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="E78">
-        <v>1.934894844676784</v>
+        <v>1.954320661395293</v>
       </c>
       <c r="F78">
-        <v>1.934894844676784</v>
+        <v>1.954320661395293</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="E81">
-        <v>2.649816155197802</v>
+        <v>2.675618764927773</v>
       </c>
       <c r="F81">
-        <v>2.649816155197802</v>
+        <v>2.675618764927773</v>
       </c>
       <c r="G81" t="b">
         <v>0</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="E84">
-        <v>2.813909564641482</v>
+        <v>2.840557262683072</v>
       </c>
       <c r="F84">
-        <v>2.813909564641482</v>
+        <v>2.840557262683072</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="E87">
-        <v>3.109479216028233</v>
+        <v>3.136465742415201</v>
       </c>
       <c r="F87">
-        <v>3.109479216028233</v>
+        <v>3.136465742415201</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="E90">
-        <v>2.22411821004064</v>
+        <v>2.240225814998942</v>
       </c>
       <c r="F90">
-        <v>2.22411821004064</v>
+        <v>2.240225814998942</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="E93">
-        <v>2.166949067193442</v>
+        <v>2.182972734991632</v>
       </c>
       <c r="F93">
-        <v>2.166949067193442</v>
+        <v>2.182972734991632</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="E96">
-        <v>2.122944628700361</v>
+        <v>2.138049652302416</v>
       </c>
       <c r="F96">
-        <v>2.122944628700361</v>
+        <v>2.138049652302416</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="E99">
-        <v>2.248260461194969</v>
+        <v>2.263046737644544</v>
       </c>
       <c r="F99">
-        <v>2.248260461194969</v>
+        <v>2.263046737644544</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="E102">
-        <v>2.079959923205337</v>
+        <v>2.09168872344799</v>
       </c>
       <c r="F102">
-        <v>2.079959923205337</v>
+        <v>2.09168872344799</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="E105">
-        <v>1.915935082816468</v>
+        <v>1.926947624093888</v>
       </c>
       <c r="F105">
-        <v>1.915935082816468</v>
+        <v>1.926947624093888</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="E108">
-        <v>1.777102984534691</v>
+        <v>1.788150228525558</v>
       </c>
       <c r="F108">
-        <v>1.777102984534691</v>
+        <v>1.788150228525558</v>
       </c>
       <c r="G108" t="b">
         <v>0</v>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="E111">
-        <v>2.217661032751813</v>
+        <v>2.233394395784741</v>
       </c>
       <c r="F111">
-        <v>2.217661032751813</v>
+        <v>2.233394395784741</v>
       </c>
       <c r="G111" t="b">
         <v>0</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="E114">
-        <v>2.353908402361604</v>
+        <v>2.373714506770277</v>
       </c>
       <c r="F114">
-        <v>2.353908402361604</v>
+        <v>2.373714506770277</v>
       </c>
       <c r="G114" t="b">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="E117">
-        <v>1.941289013054116</v>
+        <v>1.959774750260951</v>
       </c>
       <c r="F117">
-        <v>1.941289013054116</v>
+        <v>1.959774750260951</v>
       </c>
       <c r="G117" t="b">
         <v>0</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="E120">
-        <v>2.396046512430307</v>
+        <v>2.421535753154294</v>
       </c>
       <c r="F120">
-        <v>2.396046512430307</v>
+        <v>2.421535753154294</v>
       </c>
       <c r="G120" t="b">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="E123">
-        <v>1.821689186026019</v>
+        <v>1.841787961603138</v>
       </c>
       <c r="F123">
-        <v>1.821689186026019</v>
+        <v>1.841787961603138</v>
       </c>
       <c r="G123" t="b">
         <v>0</v>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="E126">
-        <v>2.254174857134624</v>
+        <v>2.277376058371245</v>
       </c>
       <c r="F126">
-        <v>2.254174857134624</v>
+        <v>2.277376058371245</v>
       </c>
       <c r="G126" t="b">
         <v>0</v>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="E129">
-        <v>1.798585379779404</v>
+        <v>1.814253755478215</v>
       </c>
       <c r="F129">
-        <v>1.798585379779404</v>
+        <v>1.814253755478215</v>
       </c>
       <c r="G129" t="b">
         <v>0</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="E132">
-        <v>1.73295984722554</v>
+        <v>1.746104620606403</v>
       </c>
       <c r="F132">
-        <v>1.73295984722554</v>
+        <v>1.746104620606403</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="E135">
-        <v>1.885650539306043</v>
+        <v>1.896131258257814</v>
       </c>
       <c r="F135">
-        <v>1.885650539306043</v>
+        <v>1.896131258257814</v>
       </c>
       <c r="G135" t="b">
         <v>0</v>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="E138">
-        <v>1.974838316714051</v>
+        <v>1.984943710485428</v>
       </c>
       <c r="F138">
-        <v>1.974838316714051</v>
+        <v>1.984943710485428</v>
       </c>
       <c r="G138" t="b">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="E141">
-        <v>1.836768886292428</v>
+        <v>1.846514368654423</v>
       </c>
       <c r="F141">
-        <v>1.836768886292428</v>
+        <v>1.846514368654423</v>
       </c>
       <c r="G141" t="b">
         <v>0</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="E144">
-        <v>1.965595923762185</v>
+        <v>1.97742594239881</v>
       </c>
       <c r="F144">
-        <v>1.965595923762185</v>
+        <v>1.97742594239881</v>
       </c>
       <c r="G144" t="b">
         <v>0</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="E147">
-        <v>2.581601080189506</v>
+        <v>2.598836289965936</v>
       </c>
       <c r="F147">
-        <v>2.581601080189506</v>
+        <v>2.598836289965936</v>
       </c>
       <c r="G147" t="b">
         <v>0</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="E150">
-        <v>2.018797141582719</v>
+        <v>2.034534796108066</v>
       </c>
       <c r="F150">
-        <v>2.018797141582719</v>
+        <v>2.034534796108066</v>
       </c>
       <c r="G150" t="b">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="E153">
-        <v>2.090411605266977</v>
+        <v>2.108065972034321</v>
       </c>
       <c r="F153">
-        <v>2.090411605266977</v>
+        <v>2.108065972034321</v>
       </c>
       <c r="G153" t="b">
         <v>0</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="E156">
-        <v>1.875554774763328</v>
+        <v>1.892186282545067</v>
       </c>
       <c r="F156">
-        <v>1.875554774763328</v>
+        <v>1.892186282545067</v>
       </c>
       <c r="G156" t="b">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="E159">
-        <v>1.797837582211089</v>
+        <v>1.814679839017439</v>
       </c>
       <c r="F159">
-        <v>1.797837582211089</v>
+        <v>1.814679839017439</v>
       </c>
       <c r="G159" t="b">
         <v>0</v>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="E162">
-        <v>1.731517887370208</v>
+        <v>1.74891066778882</v>
       </c>
       <c r="F162">
-        <v>1.731517887370208</v>
+        <v>1.74891066778882</v>
       </c>
       <c r="G162" t="b">
         <v>0</v>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="E165">
-        <v>2.100821469554435</v>
+        <v>2.120330401554</v>
       </c>
       <c r="F165">
-        <v>2.100821469554435</v>
+        <v>2.120330401554</v>
       </c>
       <c r="G165" t="b">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="E168">
-        <v>1.673022790183365</v>
+        <v>1.688435976152483</v>
       </c>
       <c r="F168">
-        <v>1.673022790183365</v>
+        <v>1.688435976152483</v>
       </c>
       <c r="G168" t="b">
         <v>0</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="E171">
-        <v>1.616599955842762</v>
+        <v>1.630118932406393</v>
       </c>
       <c r="F171">
-        <v>1.616599955842762</v>
+        <v>1.630118932406393</v>
       </c>
       <c r="G171" t="b">
         <v>0</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="E174">
-        <v>1.836856067932882</v>
+        <v>1.852292802842215</v>
       </c>
       <c r="F174">
-        <v>1.836856067932882</v>
+        <v>1.852292802842215</v>
       </c>
       <c r="G174" t="b">
         <v>0</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="E177">
-        <v>1.521987513925919</v>
+        <v>1.53398306816136</v>
       </c>
       <c r="F177">
-        <v>1.521987513925919</v>
+        <v>1.53398306816136</v>
       </c>
       <c r="G177" t="b">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="E180">
-        <v>2.220700577561738</v>
+        <v>2.237952218752936</v>
       </c>
       <c r="F180">
-        <v>2.220700577561738</v>
+        <v>2.237952218752936</v>
       </c>
       <c r="G180" t="b">
         <v>0</v>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="E183">
-        <v>1.843310778178481</v>
+        <v>1.856328487477779</v>
       </c>
       <c r="F183">
-        <v>1.843310778178481</v>
+        <v>1.856328487477779</v>
       </c>
       <c r="G183" t="b">
         <v>0</v>
@@ -5754,10 +5754,10 @@
         </is>
       </c>
       <c r="E186">
-        <v>1.77448537648492</v>
+        <v>1.785455503226968</v>
       </c>
       <c r="F186">
-        <v>1.77448537648492</v>
+        <v>1.785455503226968</v>
       </c>
       <c r="G186" t="b">
         <v>0</v>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="E189">
-        <v>1.294558801141484</v>
+        <v>1.3003956052744</v>
       </c>
       <c r="F189">
-        <v>1.294558801141484</v>
+        <v>1.3003956052744</v>
       </c>
       <c r="G189" t="b">
         <v>0</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="E192">
-        <v>1.493312875502959</v>
+        <v>1.498434227340329</v>
       </c>
       <c r="F192">
-        <v>1.493312875502959</v>
+        <v>1.498434227340329</v>
       </c>
       <c r="G192" t="b">
         <v>0</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="E195">
-        <v>1.393374948272048</v>
+        <v>1.397283738417789</v>
       </c>
       <c r="F195">
-        <v>1.393374948272048</v>
+        <v>1.397283738417789</v>
       </c>
       <c r="G195" t="b">
         <v>0</v>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="E198">
-        <v>1.276856165341282</v>
+        <v>1.280004766284699</v>
       </c>
       <c r="F198">
-        <v>1.276856165341282</v>
+        <v>1.280004766284699</v>
       </c>
       <c r="G198" t="b">
         <v>0</v>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="E201">
-        <v>1.583286277725535</v>
+        <v>1.587247241270087</v>
       </c>
       <c r="F201">
-        <v>1.583286277725535</v>
+        <v>1.587247241270087</v>
       </c>
       <c r="G201" t="b">
         <v>0</v>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="E204">
-        <v>1.567333053640564</v>
+        <v>1.570954436444389</v>
       </c>
       <c r="F204">
-        <v>1.567333053640564</v>
+        <v>1.570954436444389</v>
       </c>
       <c r="G204" t="b">
         <v>0</v>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="E207">
-        <v>1.281092880954712</v>
+        <v>1.284023283014304</v>
       </c>
       <c r="F207">
-        <v>1.281092880954712</v>
+        <v>1.284023283014304</v>
       </c>
       <c r="G207" t="b">
         <v>0</v>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="E210">
-        <v>1.275285633918078</v>
+        <v>1.2784487810703</v>
       </c>
       <c r="F210">
-        <v>1.275285633918078</v>
+        <v>1.2784487810703</v>
       </c>
       <c r="G210" t="b">
         <v>0</v>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="E213">
-        <v>1.154321422880599</v>
+        <v>1.156938872304478</v>
       </c>
       <c r="F213">
-        <v>1.154321422880599</v>
+        <v>1.156938872304478</v>
       </c>
       <c r="G213" t="b">
         <v>0</v>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="E216">
-        <v>1.473160522315679</v>
+        <v>1.476245876318905</v>
       </c>
       <c r="F216">
-        <v>1.473160522315679</v>
+        <v>1.476245876318905</v>
       </c>
       <c r="G216" t="b">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="E219">
-        <v>1.752767245910133</v>
+        <v>1.773436071859458</v>
       </c>
       <c r="F219">
-        <v>1.752767245910133</v>
+        <v>1.773436071859458</v>
       </c>
       <c r="G219" t="b">
         <v>0</v>
@@ -6798,10 +6798,10 @@
         </is>
       </c>
       <c r="E222">
-        <v>1.58513954204476</v>
+        <v>1.603886012386234</v>
       </c>
       <c r="F222">
-        <v>1.58513954204476</v>
+        <v>1.603886012386234</v>
       </c>
       <c r="G222" t="b">
         <v>0</v>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="E225">
-        <v>1.550497014556226</v>
+        <v>1.569286368498054</v>
       </c>
       <c r="F225">
-        <v>1.550497014556226</v>
+        <v>1.569286368498054</v>
       </c>
       <c r="G225" t="b">
         <v>0</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="E228">
-        <v>1.629729358691489</v>
+        <v>1.64895373948217</v>
       </c>
       <c r="F228">
-        <v>1.629729358691489</v>
+        <v>1.64895373948217</v>
       </c>
       <c r="G228" t="b">
         <v>0</v>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="E231">
-        <v>1.328349982819992</v>
+        <v>1.342700263734641</v>
       </c>
       <c r="F231">
-        <v>1.328349982819992</v>
+        <v>1.342700263734641</v>
       </c>
       <c r="G231" t="b">
         <v>0</v>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="E234">
-        <v>1.422158846874284</v>
+        <v>1.43590326600554</v>
       </c>
       <c r="F234">
-        <v>1.422158846874284</v>
+        <v>1.43590326600554</v>
       </c>
       <c r="G234" t="b">
         <v>0</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="E237">
-        <v>1.365529324441153</v>
+        <v>1.378669022721514</v>
       </c>
       <c r="F237">
-        <v>1.365529324441153</v>
+        <v>1.378669022721514</v>
       </c>
       <c r="G237" t="b">
         <v>0</v>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="E240">
-        <v>1.286635902328444</v>
+        <v>1.300352188437289</v>
       </c>
       <c r="F240">
-        <v>1.286635902328444</v>
+        <v>1.300352188437289</v>
       </c>
       <c r="G240" t="b">
         <v>0</v>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="E243">
-        <v>1.268245326855892</v>
+        <v>1.280845049970438</v>
       </c>
       <c r="F243">
-        <v>1.268245326855892</v>
+        <v>1.280845049970438</v>
       </c>
       <c r="G243" t="b">
         <v>0</v>
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="E246">
-        <v>1.79387978288316</v>
+        <v>1.812830845660455</v>
       </c>
       <c r="F246">
-        <v>1.79387978288316</v>
+        <v>1.812830845660455</v>
       </c>
       <c r="G246" t="b">
         <v>0</v>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="E249">
-        <v>1.879847989096314</v>
+        <v>1.900710875174123</v>
       </c>
       <c r="F249">
-        <v>1.879847989096314</v>
+        <v>1.900710875174123</v>
       </c>
       <c r="G249" t="b">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="E252">
-        <v>1.260489679230396</v>
+        <v>1.275155628862708</v>
       </c>
       <c r="F252">
-        <v>1.260489679230396</v>
+        <v>1.275155628862708</v>
       </c>
       <c r="G252" t="b">
         <v>0</v>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="E255">
-        <v>1.741288800938487</v>
+        <v>1.760815461798447</v>
       </c>
       <c r="F255">
-        <v>1.741288800938487</v>
+        <v>1.760815461798447</v>
       </c>
       <c r="G255" t="b">
         <v>0</v>
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="E258">
-        <v>1.442991512925688</v>
+        <v>1.456478143330321</v>
       </c>
       <c r="F258">
-        <v>1.442991512925688</v>
+        <v>1.456478143330321</v>
       </c>
       <c r="G258" t="b">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="E261">
-        <v>5.662319481228841</v>
+        <v>5.700041387193057</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="E264">
-        <v>111.2708250757248</v>
+        <v>112.3820020235143</v>
       </c>
       <c r="F264">
         <v>5</v>
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E267">
-        <v>1102.481539289447</v>
+        <v>1112.601203766963</v>
       </c>
       <c r="F267">
         <v>5</v>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="E270">
-        <v>73.37987605728601</v>
+        <v>74.03656530463566</v>
       </c>
       <c r="F270">
         <v>5</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="E273">
-        <v>10.40307855036858</v>
+        <v>10.49867902130313</v>
       </c>
       <c r="F273">
         <v>5</v>
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="E276">
-        <v>3.697640541903351</v>
+        <v>3.734573871716095</v>
       </c>
       <c r="F276">
-        <v>3.697640541903351</v>
+        <v>3.734573871716095</v>
       </c>
       <c r="G276" t="b">
         <v>0</v>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="E279">
-        <v>2.062868480720293</v>
+        <v>2.083293666587169</v>
       </c>
       <c r="F279">
-        <v>2.062868480720293</v>
+        <v>2.083293666587169</v>
       </c>
       <c r="G279" t="b">
         <v>0</v>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="E282">
-        <v>2.271587983187508</v>
+        <v>2.294486146344004</v>
       </c>
       <c r="F282">
-        <v>2.271587983187508</v>
+        <v>2.294486146344004</v>
       </c>
       <c r="G282" t="b">
         <v>0</v>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="E285">
-        <v>1.948049260970652</v>
+        <v>1.968495405642908</v>
       </c>
       <c r="F285">
-        <v>1.948049260970652</v>
+        <v>1.968495405642908</v>
       </c>
       <c r="G285" t="b">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="E288">
-        <v>1.866700990313396</v>
+        <v>1.887232109583044</v>
       </c>
       <c r="F288">
-        <v>1.866700990313396</v>
+        <v>1.887232109583044</v>
       </c>
       <c r="G288" t="b">
         <v>0</v>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="E291">
-        <v>2.113224413632166</v>
+        <v>2.137440241100708</v>
       </c>
       <c r="F291">
-        <v>2.113224413632166</v>
+        <v>2.137440241100708</v>
       </c>
       <c r="G291" t="b">
         <v>0</v>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="E294">
-        <v>1.904559282110374</v>
+        <v>1.925885553158487</v>
       </c>
       <c r="F294">
-        <v>1.904559282110374</v>
+        <v>1.925885553158487</v>
       </c>
       <c r="G294" t="b">
         <v>0</v>
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="E297">
-        <v>1.656293809585663</v>
+        <v>1.674355215256656</v>
       </c>
       <c r="F297">
-        <v>1.656293809585663</v>
+        <v>1.674355215256656</v>
       </c>
       <c r="G297" t="b">
         <v>0</v>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="E300">
-        <v>2.444558474664376</v>
+        <v>2.471170639814442</v>
       </c>
       <c r="F300">
-        <v>2.444558474664376</v>
+        <v>2.471170639814442</v>
       </c>
       <c r="G300" t="b">
         <v>0</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="E303">
-        <v>2.953172995391931</v>
+        <v>2.977354297205754</v>
       </c>
       <c r="F303">
-        <v>2.953172995391931</v>
+        <v>2.977354297205754</v>
       </c>
       <c r="G303" t="b">
         <v>0</v>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="E306">
-        <v>3.240596231836718</v>
+        <v>3.270682576717438</v>
       </c>
       <c r="F306">
-        <v>3.240596231836718</v>
+        <v>3.270682576717438</v>
       </c>
       <c r="G306" t="b">
         <v>0</v>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="E309">
-        <v>2.126448520116243</v>
+        <v>2.145574421625384</v>
       </c>
       <c r="F309">
-        <v>2.126448520116243</v>
+        <v>2.145574421625384</v>
       </c>
       <c r="G309" t="b">
         <v>0</v>
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="E312">
-        <v>1.768119571863515</v>
+        <v>1.783060759280485</v>
       </c>
       <c r="F312">
-        <v>1.768119571863515</v>
+        <v>1.783060759280485</v>
       </c>
       <c r="G312" t="b">
         <v>0</v>
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="E315">
-        <v>1.698487003349909</v>
+        <v>1.711408469265619</v>
       </c>
       <c r="F315">
-        <v>1.698487003349909</v>
+        <v>1.711408469265619</v>
       </c>
       <c r="G315" t="b">
         <v>0</v>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="E318">
-        <v>2.126429762430605</v>
+        <v>2.141221202027782</v>
       </c>
       <c r="F318">
-        <v>2.126429762430605</v>
+        <v>2.141221202027782</v>
       </c>
       <c r="G318" t="b">
         <v>0</v>
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="E321">
-        <v>1.960641031730686</v>
+        <v>1.974069762221946</v>
       </c>
       <c r="F321">
-        <v>1.960641031730686</v>
+        <v>1.974069762221946</v>
       </c>
       <c r="G321" t="b">
         <v>0</v>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="E324">
-        <v>1.794277213623928</v>
+        <v>1.807049601325858</v>
       </c>
       <c r="F324">
-        <v>1.794277213623928</v>
+        <v>1.807049601325858</v>
       </c>
       <c r="G324" t="b">
         <v>0</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E327">
-        <v>2.839262857113837</v>
+        <v>2.860047191814301</v>
       </c>
       <c r="F327">
-        <v>2.839262857113837</v>
+        <v>2.860047191814301</v>
       </c>
       <c r="G327" t="b">
         <v>0</v>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="E330">
-        <v>2.077706076833422</v>
+        <v>2.094974333445271</v>
       </c>
       <c r="F330">
-        <v>2.077706076833422</v>
+        <v>2.094974333445271</v>
       </c>
       <c r="G330" t="b">
         <v>0</v>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="E333">
-        <v>1.754333213606355</v>
+        <v>1.770026174578591</v>
       </c>
       <c r="F333">
-        <v>1.754333213606355</v>
+        <v>1.770026174578591</v>
       </c>
       <c r="G333" t="b">
         <v>0</v>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="E336">
-        <v>1.494295190882625</v>
+        <v>1.509280073370747</v>
       </c>
       <c r="F336">
-        <v>1.494295190882625</v>
+        <v>1.509280073370747</v>
       </c>
       <c r="G336" t="b">
         <v>0</v>
@@ -10191,10 +10191,10 @@
         </is>
       </c>
       <c r="E339">
-        <v>2.176621545058533</v>
+        <v>2.196649432990216</v>
       </c>
       <c r="F339">
-        <v>2.176621545058533</v>
+        <v>2.196649432990216</v>
       </c>
       <c r="G339" t="b">
         <v>0</v>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="E342">
-        <v>1.853769937980836</v>
+        <v>1.866983330587652</v>
       </c>
       <c r="F342">
-        <v>1.853769937980836</v>
+        <v>1.866983330587652</v>
       </c>
       <c r="G342" t="b">
         <v>0</v>
@@ -10365,10 +10365,10 @@
         </is>
       </c>
       <c r="E345">
-        <v>1.952924735543156</v>
+        <v>1.962906819409756</v>
       </c>
       <c r="F345">
-        <v>1.952924735543156</v>
+        <v>1.962906819409756</v>
       </c>
       <c r="G345" t="b">
         <v>0</v>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="E348">
-        <v>1.765144124213947</v>
+        <v>1.770822306777751</v>
       </c>
       <c r="F348">
-        <v>1.765144124213947</v>
+        <v>1.770822306777751</v>
       </c>
       <c r="G348" t="b">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         </is>
       </c>
       <c r="E351">
-        <v>2.03615002420113</v>
+        <v>2.043949384491898</v>
       </c>
       <c r="F351">
-        <v>2.03615002420113</v>
+        <v>2.043949384491898</v>
       </c>
       <c r="G351" t="b">
         <v>0</v>
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="E354">
-        <v>1.631143554090404</v>
+        <v>1.637785555327613</v>
       </c>
       <c r="F354">
-        <v>1.631143554090404</v>
+        <v>1.637785555327613</v>
       </c>
       <c r="G354" t="b">
         <v>0</v>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="E357">
-        <v>1.864005640252844</v>
+        <v>1.872907079980026</v>
       </c>
       <c r="F357">
-        <v>1.864005640252844</v>
+        <v>1.872907079980026</v>
       </c>
       <c r="G357" t="b">
         <v>0</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="E360">
-        <v>2.015707908173348</v>
+        <v>2.025739585956179</v>
       </c>
       <c r="F360">
-        <v>2.015707908173348</v>
+        <v>2.025739585956179</v>
       </c>
       <c r="G360" t="b">
         <v>0</v>
@@ -10887,10 +10887,10 @@
         </is>
       </c>
       <c r="E363">
-        <v>2.421045215564263</v>
+        <v>2.433802904895924</v>
       </c>
       <c r="F363">
-        <v>2.421045215564263</v>
+        <v>2.433802904895924</v>
       </c>
       <c r="G363" t="b">
         <v>0</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="E366">
-        <v>2.091842735868035</v>
+        <v>2.104112991320461</v>
       </c>
       <c r="F366">
-        <v>2.091842735868035</v>
+        <v>2.104112991320461</v>
       </c>
       <c r="G366" t="b">
         <v>0</v>
@@ -11061,10 +11061,10 @@
         </is>
       </c>
       <c r="E369">
-        <v>2.556992517513003</v>
+        <v>2.573489172914989</v>
       </c>
       <c r="F369">
-        <v>2.556992517513003</v>
+        <v>2.573489172914989</v>
       </c>
       <c r="G369" t="b">
         <v>0</v>
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="E372">
-        <v>2.069289730800475</v>
+        <v>2.084329788038746</v>
       </c>
       <c r="F372">
-        <v>2.069289730800475</v>
+        <v>2.084329788038746</v>
       </c>
       <c r="G372" t="b">
         <v>0</v>
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="E375">
-        <v>1.870138841888211</v>
+        <v>1.883897892192228</v>
       </c>
       <c r="F375">
-        <v>1.870138841888211</v>
+        <v>1.883897892192228</v>
       </c>
       <c r="G375" t="b">
         <v>0</v>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="E378">
-        <v>1.904811159211777</v>
+        <v>1.918547812373622</v>
       </c>
       <c r="F378">
-        <v>1.904811159211777</v>
+        <v>1.918547812373622</v>
       </c>
       <c r="G378" t="b">
         <v>0</v>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="E381">
-        <v>2.292674180513982</v>
+        <v>2.30822607187858</v>
       </c>
       <c r="F381">
-        <v>2.292674180513982</v>
+        <v>2.30822607187858</v>
       </c>
       <c r="G381" t="b">
         <v>0</v>
@@ -11496,10 +11496,10 @@
         </is>
       </c>
       <c r="E384">
-        <v>2.315396823412147</v>
+        <v>2.330704479877136</v>
       </c>
       <c r="F384">
-        <v>2.315396823412147</v>
+        <v>2.330704479877136</v>
       </c>
       <c r="G384" t="b">
         <v>0</v>
@@ -11583,10 +11583,10 @@
         </is>
       </c>
       <c r="E387">
-        <v>2.171243010178174</v>
+        <v>2.185581534059747</v>
       </c>
       <c r="F387">
-        <v>2.171243010178174</v>
+        <v>2.185581534059747</v>
       </c>
       <c r="G387" t="b">
         <v>0</v>
@@ -11670,10 +11670,10 @@
         </is>
       </c>
       <c r="E390">
-        <v>2.106107263281347</v>
+        <v>2.12127089654683</v>
       </c>
       <c r="F390">
-        <v>2.106107263281347</v>
+        <v>2.12127089654683</v>
       </c>
       <c r="G390" t="b">
         <v>0</v>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="E393">
-        <v>2.600543037145722</v>
+        <v>2.61825744184735</v>
       </c>
       <c r="F393">
-        <v>2.600543037145722</v>
+        <v>2.61825744184735</v>
       </c>
       <c r="G393" t="b">
         <v>0</v>
@@ -11844,10 +11844,10 @@
         </is>
       </c>
       <c r="E396">
-        <v>2.76459695406932</v>
+        <v>2.782353812633295</v>
       </c>
       <c r="F396">
-        <v>2.76459695406932</v>
+        <v>2.782353812633295</v>
       </c>
       <c r="G396" t="b">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         </is>
       </c>
       <c r="E399">
-        <v>2.207848419183092</v>
+        <v>2.220503062412595</v>
       </c>
       <c r="F399">
-        <v>2.207848419183092</v>
+        <v>2.220503062412595</v>
       </c>
       <c r="G399" t="b">
         <v>0</v>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="E402">
-        <v>2.699697628428203</v>
+        <v>2.708273187582499</v>
       </c>
       <c r="F402">
-        <v>2.699697628428203</v>
+        <v>2.708273187582499</v>
       </c>
       <c r="G402" t="b">
         <v>0</v>
@@ -12105,10 +12105,10 @@
         </is>
       </c>
       <c r="E405">
-        <v>2.644497776308823</v>
+        <v>2.647473268237016</v>
       </c>
       <c r="F405">
-        <v>2.644497776308823</v>
+        <v>2.647473268237016</v>
       </c>
       <c r="G405" t="b">
         <v>0</v>
@@ -12192,10 +12192,10 @@
         </is>
       </c>
       <c r="E408">
-        <v>2.57609901591704</v>
+        <v>2.576908939048826</v>
       </c>
       <c r="F408">
-        <v>2.57609901591704</v>
+        <v>2.576908939048826</v>
       </c>
       <c r="G408" t="b">
         <v>0</v>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="E411">
-        <v>1.871507421671887</v>
+        <v>1.872134239840509</v>
       </c>
       <c r="F411">
-        <v>1.871507421671887</v>
+        <v>1.872134239840509</v>
       </c>
       <c r="G411" t="b">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         </is>
       </c>
       <c r="E414">
-        <v>2.434302083731776</v>
+        <v>2.43864640973503</v>
       </c>
       <c r="F414">
-        <v>2.434302083731776</v>
+        <v>2.43864640973503</v>
       </c>
       <c r="G414" t="b">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         </is>
       </c>
       <c r="E417">
-        <v>2.167385719752432</v>
+        <v>2.171032568268457</v>
       </c>
       <c r="F417">
-        <v>2.167385719752432</v>
+        <v>2.171032568268457</v>
       </c>
       <c r="G417" t="b">
         <v>0</v>
@@ -12540,10 +12540,10 @@
         </is>
       </c>
       <c r="E420">
-        <v>2.146859385926744</v>
+        <v>2.148925210591319</v>
       </c>
       <c r="F420">
-        <v>2.146859385926744</v>
+        <v>2.148925210591319</v>
       </c>
       <c r="G420" t="b">
         <v>0</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="E423">
-        <v>2.523676672606453</v>
+        <v>2.523817802064734</v>
       </c>
       <c r="F423">
-        <v>2.523676672606453</v>
+        <v>2.523817802064734</v>
       </c>
       <c r="G423" t="b">
         <v>0</v>
@@ -12714,10 +12714,10 @@
         </is>
       </c>
       <c r="E426">
-        <v>2.547856480156835</v>
+        <v>2.548601658537998</v>
       </c>
       <c r="F426">
-        <v>2.547856480156835</v>
+        <v>2.548601658537998</v>
       </c>
       <c r="G426" t="b">
         <v>0</v>
@@ -12801,10 +12801,10 @@
         </is>
       </c>
       <c r="E429">
-        <v>1.738719844609237</v>
+        <v>1.74047711544535</v>
       </c>
       <c r="F429">
-        <v>1.738719844609237</v>
+        <v>1.74047711544535</v>
       </c>
       <c r="G429" t="b">
         <v>0</v>
@@ -12888,10 +12888,10 @@
         </is>
       </c>
       <c r="E432">
-        <v>2.454041725981179</v>
+        <v>2.45908958725364</v>
       </c>
       <c r="F432">
-        <v>2.454041725981179</v>
+        <v>2.45908958725364</v>
       </c>
       <c r="G432" t="b">
         <v>0</v>
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>1.561809693986961</v>
+        <v>1.577188313897582</v>
       </c>
       <c r="F435">
-        <v>1.561809693986961</v>
+        <v>1.577188313897582</v>
       </c>
       <c r="G435" t="b">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         </is>
       </c>
       <c r="E438">
-        <v>1.534274717669098</v>
+        <v>1.549670213541193</v>
       </c>
       <c r="F438">
-        <v>1.534274717669098</v>
+        <v>1.549670213541193</v>
       </c>
       <c r="G438" t="b">
         <v>0</v>
@@ -13149,10 +13149,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>1.402744615712108</v>
+        <v>1.417062985861836</v>
       </c>
       <c r="F441">
-        <v>1.402744615712108</v>
+        <v>1.417062985861836</v>
       </c>
       <c r="G441" t="b">
         <v>0</v>
@@ -13236,10 +13236,10 @@
         </is>
       </c>
       <c r="E444">
-        <v>1.383778266407165</v>
+        <v>1.397320001306184</v>
       </c>
       <c r="F444">
-        <v>1.383778266407165</v>
+        <v>1.397320001306184</v>
       </c>
       <c r="G444" t="b">
         <v>0</v>
@@ -13323,10 +13323,10 @@
         </is>
       </c>
       <c r="E447">
-        <v>1.503865760393201</v>
+        <v>1.516294353096004</v>
       </c>
       <c r="F447">
-        <v>1.503865760393201</v>
+        <v>1.516294353096004</v>
       </c>
       <c r="G447" t="b">
         <v>0</v>
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="E450">
-        <v>1.364362801356498</v>
+        <v>1.374524448369565</v>
       </c>
       <c r="F450">
-        <v>1.364362801356498</v>
+        <v>1.374524448369565</v>
       </c>
       <c r="G450" t="b">
         <v>0</v>
@@ -13497,10 +13497,10 @@
         </is>
       </c>
       <c r="E453">
-        <v>1.33006061490399</v>
+        <v>1.34141605887158</v>
       </c>
       <c r="F453">
-        <v>1.33006061490399</v>
+        <v>1.34141605887158</v>
       </c>
       <c r="G453" t="b">
         <v>0</v>
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="E456">
-        <v>1.331468114705955</v>
+        <v>1.342589619069089</v>
       </c>
       <c r="F456">
-        <v>1.331468114705955</v>
+        <v>1.342589619069089</v>
       </c>
       <c r="G456" t="b">
         <v>0</v>
@@ -13671,10 +13671,10 @@
         </is>
       </c>
       <c r="E459">
-        <v>1.394221538004739</v>
+        <v>1.405872152583937</v>
       </c>
       <c r="F459">
-        <v>1.394221538004739</v>
+        <v>1.405872152583937</v>
       </c>
       <c r="G459" t="b">
         <v>0</v>
@@ -13758,10 +13758,10 @@
         </is>
       </c>
       <c r="E462">
-        <v>1.12108835495456</v>
+        <v>1.131286119970693</v>
       </c>
       <c r="F462">
-        <v>1.12108835495456</v>
+        <v>1.131286119970693</v>
       </c>
       <c r="G462" t="b">
         <v>0</v>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="E465">
-        <v>1.1648250569645</v>
+        <v>1.175194457652167</v>
       </c>
       <c r="F465">
-        <v>1.1648250569645</v>
+        <v>1.175194457652167</v>
       </c>
       <c r="G465" t="b">
         <v>0</v>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="E468">
-        <v>1.320758166535855</v>
+        <v>1.334315646287876</v>
       </c>
       <c r="F468">
-        <v>1.320758166535855</v>
+        <v>1.334315646287876</v>
       </c>
       <c r="G468" t="b">
         <v>0</v>
@@ -14019,10 +14019,10 @@
         </is>
       </c>
       <c r="E471">
-        <v>1.146781737497777</v>
+        <v>1.158992366078434</v>
       </c>
       <c r="F471">
-        <v>1.146781737497777</v>
+        <v>1.158992366078434</v>
       </c>
       <c r="G471" t="b">
         <v>0</v>
@@ -14106,10 +14106,10 @@
         </is>
       </c>
       <c r="E474">
-        <v>1.478543194368125</v>
+        <v>1.49455204665305</v>
       </c>
       <c r="F474">
-        <v>1.478543194368125</v>
+        <v>1.49455204665305</v>
       </c>
       <c r="G474" t="b">
         <v>0</v>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="E477">
-        <v>3.141722382684421</v>
+        <v>3.159472481611594</v>
       </c>
       <c r="F477">
-        <v>3.141722382684421</v>
+        <v>3.159472481611594</v>
       </c>
       <c r="G477" t="b">
         <v>0</v>
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="E480">
-        <v>7.616039361626079</v>
+        <v>7.679525344806037</v>
       </c>
       <c r="F480">
         <v>5</v>
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="E483">
-        <v>20.87746590434395</v>
+        <v>21.04857570128651</v>
       </c>
       <c r="F483">
         <v>5</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="E486">
-        <v>10.80250260034073</v>
+        <v>10.89017342952132</v>
       </c>
       <c r="F486">
         <v>5</v>
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="E489">
-        <v>8.317800721982127</v>
+        <v>8.383906292885397</v>
       </c>
       <c r="F489">
         <v>5</v>
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="E492">
-        <v>3.114130707136201</v>
+        <v>3.138623355675338</v>
       </c>
       <c r="F492">
-        <v>3.114130707136201</v>
+        <v>3.138623355675338</v>
       </c>
       <c r="G492" t="b">
         <v>0</v>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="E495">
-        <v>2.198783744404223</v>
+        <v>2.21537796644314</v>
       </c>
       <c r="F495">
-        <v>2.198783744404223</v>
+        <v>2.21537796644314</v>
       </c>
       <c r="G495" t="b">
         <v>0</v>
@@ -14802,10 +14802,10 @@
         </is>
       </c>
       <c r="E498">
-        <v>1.764478080169122</v>
+        <v>1.778613788341264</v>
       </c>
       <c r="F498">
-        <v>1.764478080169122</v>
+        <v>1.778613788341264</v>
       </c>
       <c r="G498" t="b">
         <v>0</v>
@@ -14889,10 +14889,10 @@
         </is>
       </c>
       <c r="E501">
-        <v>1.714813247318962</v>
+        <v>1.730038260555377</v>
       </c>
       <c r="F501">
-        <v>1.714813247318962</v>
+        <v>1.730038260555377</v>
       </c>
       <c r="G501" t="b">
         <v>0</v>
@@ -14976,10 +14976,10 @@
         </is>
       </c>
       <c r="E504">
-        <v>1.624609232414467</v>
+        <v>1.639420388212161</v>
       </c>
       <c r="F504">
-        <v>1.624609232414467</v>
+        <v>1.639420388212161</v>
       </c>
       <c r="G504" t="b">
         <v>0</v>
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="E507">
-        <v>1.496362718717235</v>
+        <v>1.510075777549617</v>
       </c>
       <c r="F507">
-        <v>1.496362718717235</v>
+        <v>1.510075777549617</v>
       </c>
       <c r="G507" t="b">
         <v>0</v>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="E510">
-        <v>1.731538420816893</v>
+        <v>1.748292124315828</v>
       </c>
       <c r="F510">
-        <v>1.731538420816893</v>
+        <v>1.748292124315828</v>
       </c>
       <c r="G510" t="b">
         <v>0</v>
@@ -15237,10 +15237,10 @@
         </is>
       </c>
       <c r="E513">
-        <v>1.744281285357032</v>
+        <v>1.762294071817743</v>
       </c>
       <c r="F513">
-        <v>1.744281285357032</v>
+        <v>1.762294071817743</v>
       </c>
       <c r="G513" t="b">
         <v>0</v>
@@ -15324,10 +15324,10 @@
         </is>
       </c>
       <c r="E516">
-        <v>1.835081854023862</v>
+        <v>1.852774253782987</v>
       </c>
       <c r="F516">
-        <v>1.835081854023862</v>
+        <v>1.852774253782987</v>
       </c>
       <c r="G516" t="b">
         <v>0</v>
@@ -15411,10 +15411,10 @@
         </is>
       </c>
       <c r="E519">
-        <v>1.648044075789216</v>
+        <v>1.660781126413461</v>
       </c>
       <c r="F519">
-        <v>1.648044075789216</v>
+        <v>1.660781126413461</v>
       </c>
       <c r="G519" t="b">
         <v>0</v>
@@ -15498,10 +15498,10 @@
         </is>
       </c>
       <c r="E522">
-        <v>1.814003961205593</v>
+        <v>1.824664346339077</v>
       </c>
       <c r="F522">
-        <v>1.814003961205593</v>
+        <v>1.824664346339077</v>
       </c>
       <c r="G522" t="b">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         </is>
       </c>
       <c r="E525">
-        <v>1.633685729831216</v>
+        <v>1.642308869472675</v>
       </c>
       <c r="F525">
-        <v>1.633685729831216</v>
+        <v>1.642308869472675</v>
       </c>
       <c r="G525" t="b">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="E528">
-        <v>1.786148175367771</v>
+        <v>1.794411532217616</v>
       </c>
       <c r="F528">
-        <v>1.786148175367771</v>
+        <v>1.794411532217616</v>
       </c>
       <c r="G528" t="b">
         <v>0</v>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="E531">
-        <v>1.794997898505653</v>
+        <v>1.802322118259994</v>
       </c>
       <c r="F531">
-        <v>1.794997898505653</v>
+        <v>1.802322118259994</v>
       </c>
       <c r="G531" t="b">
         <v>0</v>
@@ -15846,10 +15846,10 @@
         </is>
       </c>
       <c r="E534">
-        <v>1.69822204682293</v>
+        <v>1.70395109686103</v>
       </c>
       <c r="F534">
-        <v>1.69822204682293</v>
+        <v>1.70395109686103</v>
       </c>
       <c r="G534" t="b">
         <v>0</v>
@@ -15933,10 +15933,10 @@
         </is>
       </c>
       <c r="E537">
-        <v>1.671455408205165</v>
+        <v>1.678014608957202</v>
       </c>
       <c r="F537">
-        <v>1.671455408205165</v>
+        <v>1.678014608957202</v>
       </c>
       <c r="G537" t="b">
         <v>0</v>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="E540">
-        <v>1.965722764259906</v>
+        <v>1.974368030755421</v>
       </c>
       <c r="F540">
-        <v>1.965722764259906</v>
+        <v>1.974368030755421</v>
       </c>
       <c r="G540" t="b">
         <v>0</v>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="E543">
-        <v>2.897045620537271</v>
+        <v>2.911984587844644</v>
       </c>
       <c r="F543">
-        <v>2.897045620537271</v>
+        <v>2.911984587844644</v>
       </c>
       <c r="G543" t="b">
         <v>0</v>
@@ -16194,10 +16194,10 @@
         </is>
       </c>
       <c r="E546">
-        <v>1.756756964339095</v>
+        <v>1.767638179121717</v>
       </c>
       <c r="F546">
-        <v>1.756756964339095</v>
+        <v>1.767638179121717</v>
       </c>
       <c r="G546" t="b">
         <v>0</v>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="E549">
-        <v>1.968808314177725</v>
+        <v>1.98134340415579</v>
       </c>
       <c r="F549">
-        <v>1.968808314177725</v>
+        <v>1.98134340415579</v>
       </c>
       <c r="G549" t="b">
         <v>0</v>
@@ -16368,10 +16368,10 @@
         </is>
       </c>
       <c r="E552">
-        <v>1.650301316841078</v>
+        <v>1.662189028004291</v>
       </c>
       <c r="F552">
-        <v>1.650301316841078</v>
+        <v>1.662189028004291</v>
       </c>
       <c r="G552" t="b">
         <v>0</v>
@@ -16455,10 +16455,10 @@
         </is>
       </c>
       <c r="E555">
-        <v>1.890787908169184</v>
+        <v>1.902486687881943</v>
       </c>
       <c r="F555">
-        <v>1.890787908169184</v>
+        <v>1.902486687881943</v>
       </c>
       <c r="G555" t="b">
         <v>0</v>
@@ -16542,10 +16542,10 @@
         </is>
       </c>
       <c r="E558">
-        <v>1.537543302912694</v>
+        <v>1.544795418026422</v>
       </c>
       <c r="F558">
-        <v>1.537543302912694</v>
+        <v>1.544795418026422</v>
       </c>
       <c r="G558" t="b">
         <v>0</v>
@@ -16629,10 +16629,10 @@
         </is>
       </c>
       <c r="E561">
-        <v>1.822965297350674</v>
+        <v>1.827230407844052</v>
       </c>
       <c r="F561">
-        <v>1.822965297350674</v>
+        <v>1.827230407844052</v>
       </c>
       <c r="G561" t="b">
         <v>0</v>
@@ -16716,10 +16716,10 @@
         </is>
       </c>
       <c r="E564">
-        <v>1.741561418351858</v>
+        <v>1.746117859124362</v>
       </c>
       <c r="F564">
-        <v>1.741561418351858</v>
+        <v>1.746117859124362</v>
       </c>
       <c r="G564" t="b">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         </is>
       </c>
       <c r="E567">
-        <v>1.587315228135743</v>
+        <v>1.591368738867964</v>
       </c>
       <c r="F567">
-        <v>1.587315228135743</v>
+        <v>1.591368738867964</v>
       </c>
       <c r="G567" t="b">
         <v>0</v>
@@ -16890,10 +16890,10 @@
         </is>
       </c>
       <c r="E570">
-        <v>1.561998483255568</v>
+        <v>1.567355642080688</v>
       </c>
       <c r="F570">
-        <v>1.561998483255568</v>
+        <v>1.567355642080688</v>
       </c>
       <c r="G570" t="b">
         <v>0</v>
@@ -16977,10 +16977,10 @@
         </is>
       </c>
       <c r="E573">
-        <v>1.811214451259243</v>
+        <v>1.818508952968518</v>
       </c>
       <c r="F573">
-        <v>1.811214451259243</v>
+        <v>1.818508952968518</v>
       </c>
       <c r="G573" t="b">
         <v>0</v>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="E576">
-        <v>1.556805871271347</v>
+        <v>1.563503719242754</v>
       </c>
       <c r="F576">
-        <v>1.556805871271347</v>
+        <v>1.563503719242754</v>
       </c>
       <c r="G576" t="b">
         <v>0</v>
@@ -17151,10 +17151,10 @@
         </is>
       </c>
       <c r="E579">
-        <v>2.593350601327382</v>
+        <v>2.606414270932688</v>
       </c>
       <c r="F579">
-        <v>2.593350601327382</v>
+        <v>2.606414270932688</v>
       </c>
       <c r="G579" t="b">
         <v>0</v>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="E582">
-        <v>2.464245419699819</v>
+        <v>2.480283571995865</v>
       </c>
       <c r="F582">
-        <v>2.464245419699819</v>
+        <v>2.480283571995865</v>
       </c>
       <c r="G582" t="b">
         <v>0</v>
@@ -17325,10 +17325,10 @@
         </is>
       </c>
       <c r="E585">
-        <v>2.578537066687993</v>
+        <v>2.598142984032781</v>
       </c>
       <c r="F585">
-        <v>2.578537066687993</v>
+        <v>2.598142984032781</v>
       </c>
       <c r="G585" t="b">
         <v>0</v>
@@ -17412,10 +17412,10 @@
         </is>
       </c>
       <c r="E588">
-        <v>2.377405442221422</v>
+        <v>2.397839716762933</v>
       </c>
       <c r="F588">
-        <v>2.377405442221422</v>
+        <v>2.397839716762933</v>
       </c>
       <c r="G588" t="b">
         <v>0</v>
@@ -17499,10 +17499,10 @@
         </is>
       </c>
       <c r="E591">
-        <v>1.945418693302261</v>
+        <v>1.964202617347392</v>
       </c>
       <c r="F591">
-        <v>1.945418693302261</v>
+        <v>1.964202617347392</v>
       </c>
       <c r="G591" t="b">
         <v>0</v>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="E594">
-        <v>1.645242799177881</v>
+        <v>1.661556332735235</v>
       </c>
       <c r="F594">
-        <v>1.645242799177881</v>
+        <v>1.661556332735235</v>
       </c>
       <c r="G594" t="b">
         <v>0</v>
@@ -17673,10 +17673,10 @@
         </is>
       </c>
       <c r="E597">
-        <v>1.518396516747922</v>
+        <v>1.53320419066828</v>
       </c>
       <c r="F597">
-        <v>1.518396516747922</v>
+        <v>1.53320419066828</v>
       </c>
       <c r="G597" t="b">
         <v>0</v>
@@ -17760,10 +17760,10 @@
         </is>
       </c>
       <c r="E600">
-        <v>1.573132884436329</v>
+        <v>1.588525290321978</v>
       </c>
       <c r="F600">
-        <v>1.573132884436329</v>
+        <v>1.588525290321978</v>
       </c>
       <c r="G600" t="b">
         <v>0</v>
@@ -17847,10 +17847,10 @@
         </is>
       </c>
       <c r="E603">
-        <v>1.414319810525277</v>
+        <v>1.428562024959979</v>
       </c>
       <c r="F603">
-        <v>1.414319810525277</v>
+        <v>1.428562024959979</v>
       </c>
       <c r="G603" t="b">
         <v>0</v>
@@ -17934,10 +17934,10 @@
         </is>
       </c>
       <c r="E606">
-        <v>1.391179062657669</v>
+        <v>1.405647771253355</v>
       </c>
       <c r="F606">
-        <v>1.391179062657669</v>
+        <v>1.405647771253355</v>
       </c>
       <c r="G606" t="b">
         <v>0</v>
@@ -18021,10 +18021,10 @@
         </is>
       </c>
       <c r="E609">
-        <v>2.041949681462848</v>
+        <v>2.060763379905107</v>
       </c>
       <c r="F609">
-        <v>2.041949681462848</v>
+        <v>2.060763379905107</v>
       </c>
       <c r="G609" t="b">
         <v>0</v>
@@ -18108,10 +18108,10 @@
         </is>
       </c>
       <c r="E612">
-        <v>1.572188279889407</v>
+        <v>1.584808126670086</v>
       </c>
       <c r="F612">
-        <v>1.572188279889407</v>
+        <v>1.584808126670086</v>
       </c>
       <c r="G612" t="b">
         <v>0</v>
@@ -18195,10 +18195,10 @@
         </is>
       </c>
       <c r="E615">
-        <v>2.053323808841054</v>
+        <v>2.067777444248473</v>
       </c>
       <c r="F615">
-        <v>2.053323808841054</v>
+        <v>2.067777444248473</v>
       </c>
       <c r="G615" t="b">
         <v>0</v>
@@ -18282,10 +18282,10 @@
         </is>
       </c>
       <c r="E618">
-        <v>2.146080531407744</v>
+        <v>2.159712449209001</v>
       </c>
       <c r="F618">
-        <v>2.146080531407744</v>
+        <v>2.159712449209001</v>
       </c>
       <c r="G618" t="b">
         <v>0</v>
@@ -18369,10 +18369,10 @@
         </is>
       </c>
       <c r="E621">
-        <v>1.406840851538491</v>
+        <v>1.413637569450872</v>
       </c>
       <c r="F621">
-        <v>1.406840851538491</v>
+        <v>1.413637569450872</v>
       </c>
       <c r="G621" t="b">
         <v>0</v>
@@ -18456,10 +18456,10 @@
         </is>
       </c>
       <c r="E624">
-        <v>1.729272336545792</v>
+        <v>1.735216299247829</v>
       </c>
       <c r="F624">
-        <v>1.729272336545792</v>
+        <v>1.735216299247829</v>
       </c>
       <c r="G624" t="b">
         <v>0</v>
@@ -18543,10 +18543,10 @@
         </is>
       </c>
       <c r="E627">
-        <v>1.586474143091051</v>
+        <v>1.589829294308605</v>
       </c>
       <c r="F627">
-        <v>1.586474143091051</v>
+        <v>1.589829294308605</v>
       </c>
       <c r="G627" t="b">
         <v>0</v>
@@ -18630,10 +18630,10 @@
         </is>
       </c>
       <c r="E630">
-        <v>1.561427465819291</v>
+        <v>1.56470233861069</v>
       </c>
       <c r="F630">
-        <v>1.561427465819291</v>
+        <v>1.56470233861069</v>
       </c>
       <c r="G630" t="b">
         <v>0</v>
@@ -18717,10 +18717,10 @@
         </is>
       </c>
       <c r="E633">
-        <v>1.363861596517282</v>
+        <v>1.367233809240627</v>
       </c>
       <c r="F633">
-        <v>1.363861596517282</v>
+        <v>1.367233809240627</v>
       </c>
       <c r="G633" t="b">
         <v>0</v>
@@ -18804,10 +18804,10 @@
         </is>
       </c>
       <c r="E636">
-        <v>1.355731460996122</v>
+        <v>1.359682187783225</v>
       </c>
       <c r="F636">
-        <v>1.355731460996122</v>
+        <v>1.359682187783225</v>
       </c>
       <c r="G636" t="b">
         <v>0</v>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="E639">
-        <v>1.198507799784624</v>
+        <v>1.202123274222578</v>
       </c>
       <c r="F639">
-        <v>1.198507799784624</v>
+        <v>1.202123274222578</v>
       </c>
       <c r="G639" t="b">
         <v>0</v>
@@ -18978,10 +18978,10 @@
         </is>
       </c>
       <c r="E642">
-        <v>1.135268724850204</v>
+        <v>1.138955085664156</v>
       </c>
       <c r="F642">
-        <v>1.135268724850204</v>
+        <v>1.138955085664156</v>
       </c>
       <c r="G642" t="b">
         <v>0</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="E645">
-        <v>1.207597338185464</v>
+        <v>1.211151159388446</v>
       </c>
       <c r="F645">
-        <v>1.207597338185464</v>
+        <v>1.211151159388446</v>
       </c>
       <c r="G645" t="b">
         <v>0</v>
@@ -19152,10 +19152,10 @@
         </is>
       </c>
       <c r="E648">
-        <v>1.213367007951611</v>
+        <v>1.21591730980469</v>
       </c>
       <c r="F648">
-        <v>1.213367007951611</v>
+        <v>1.21591730980469</v>
       </c>
       <c r="G648" t="b">
         <v>0</v>
